--- a/ksoft_old/docs/records/Sales_Channel_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Channel_Records.xlsx
@@ -2654,13 +2654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3700768A-82E0-4132-8569-5F6381C70F09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932E772C-E5E8-4DD1-85CB-877BEEE4A129}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191F0DAC-CCEE-4189-BF21-87FDD5DA6E3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B67722D8-93A1-4008-B3FF-9C904018AA9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5E8B7D-A848-44F4-84E1-8903CF2C491B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F899ABAF-75C7-4CE7-A404-FBF5D45A4598}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Channel_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Channel_Records.xlsx
@@ -2654,13 +2654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932E772C-E5E8-4DD1-85CB-877BEEE4A129}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBB69022-0AA1-46AF-A613-47A09704165C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B67722D8-93A1-4008-B3FF-9C904018AA9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9770E560-1064-4D0B-9CC4-750268F6BD53}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F899ABAF-75C7-4CE7-A404-FBF5D45A4598}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F08DBE-62E5-4862-AC92-FD99B27950A4}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Channel_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Channel_Records.xlsx
@@ -2654,13 +2654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBB69022-0AA1-46AF-A613-47A09704165C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3700768A-82E0-4132-8569-5F6381C70F09}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9770E560-1064-4D0B-9CC4-750268F6BD53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191F0DAC-CCEE-4189-BF21-87FDD5DA6E3F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F08DBE-62E5-4862-AC92-FD99B27950A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5E8B7D-A848-44F4-84E1-8903CF2C491B}"/>
 </file>